--- a/AAII_Financials/Quarterly/BCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BCT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>BCT</t>
   </si>
@@ -656,95 +656,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -799,8 +803,11 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -855,8 +862,11 @@
       <c r="T9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -911,8 +921,11 @@
       <c r="T10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,64 +946,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>7100</v>
+        <v>9300</v>
       </c>
       <c r="E12" s="3">
-        <v>5300</v>
+        <v>7000</v>
       </c>
       <c r="F12" s="3">
-        <v>4200</v>
+        <v>5200</v>
       </c>
       <c r="G12" s="3">
-        <v>4500</v>
+        <v>4100</v>
       </c>
       <c r="H12" s="3">
         <v>4400</v>
       </c>
       <c r="I12" s="3">
-        <v>3500</v>
+        <v>4300</v>
       </c>
       <c r="J12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K12" s="3">
         <v>2300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,13 +1062,16 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1059,11 +1079,11 @@
       <c r="F14" s="3">
         <v>0</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1075,13 +1095,13 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M14" s="3">
         <v>200</v>
       </c>
       <c r="N14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1089,8 +1109,8 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
@@ -1101,8 +1121,11 @@
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1130,8 +1153,8 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1154,11 +1177,14 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,64 +1202,68 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10600</v>
+        <v>11500</v>
       </c>
       <c r="E17" s="3">
-        <v>7800</v>
+        <v>10400</v>
       </c>
       <c r="F17" s="3">
-        <v>6200</v>
+        <v>7700</v>
       </c>
       <c r="G17" s="3">
-        <v>7400</v>
+        <v>6100</v>
       </c>
       <c r="H17" s="3">
-        <v>7200</v>
+        <v>7300</v>
       </c>
       <c r="I17" s="3">
-        <v>6700</v>
+        <v>7100</v>
       </c>
       <c r="J17" s="3">
+        <v>6600</v>
+      </c>
+      <c r="K17" s="3">
         <v>5000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1241,55 +1271,58 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>-7800</v>
+        <v>-10400</v>
       </c>
       <c r="F18" s="3">
-        <v>-6200</v>
+        <v>-7700</v>
       </c>
       <c r="G18" s="3">
-        <v>-7400</v>
+        <v>-6100</v>
       </c>
       <c r="H18" s="3">
-        <v>-7200</v>
+        <v>-7300</v>
       </c>
       <c r="I18" s="3">
-        <v>-6700</v>
+        <v>-7100</v>
       </c>
       <c r="J18" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="K18" s="3">
         <v>-5000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,8 +1343,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1319,35 +1353,35 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F20" s="3">
         <v>1100</v>
       </c>
-      <c r="F20" s="3">
-        <v>-10200</v>
-      </c>
       <c r="G20" s="3">
-        <v>5900</v>
+        <v>-10000</v>
       </c>
       <c r="H20" s="3">
-        <v>6600</v>
+        <v>5800</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>20400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-34100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>11100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1361,13 +1395,16 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1375,60 +1412,63 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
-        <v>-6700</v>
+        <v>-3300</v>
       </c>
       <c r="F21" s="3">
-        <v>-16300</v>
+        <v>-6600</v>
       </c>
       <c r="G21" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="H21" s="3">
         <v>-1500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-600</v>
       </c>
-      <c r="I21" s="3">
-        <v>-6700</v>
-      </c>
       <c r="J21" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="K21" s="3">
         <v>15400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-37200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-18500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1900</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-1700</v>
       </c>
       <c r="T21" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -1452,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
@@ -1461,7 +1501,7 @@
         <v>100</v>
       </c>
       <c r="O22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1478,64 +1518,70 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3300</v>
       </c>
-      <c r="E23" s="3">
-        <v>-6700</v>
-      </c>
       <c r="F23" s="3">
-        <v>-16300</v>
+        <v>-6600</v>
       </c>
       <c r="G23" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="H23" s="3">
         <v>-1500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-600</v>
       </c>
-      <c r="I23" s="3">
-        <v>-6700</v>
-      </c>
       <c r="J23" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="K23" s="3">
         <v>15400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-37200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-18700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1900</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-1700</v>
       </c>
       <c r="T23" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1590,8 +1636,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3300</v>
       </c>
-      <c r="E26" s="3">
-        <v>-6700</v>
-      </c>
       <c r="F26" s="3">
-        <v>-16300</v>
+        <v>-6600</v>
       </c>
       <c r="G26" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="H26" s="3">
         <v>-1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-600</v>
       </c>
-      <c r="I26" s="3">
-        <v>-6700</v>
-      </c>
       <c r="J26" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="K26" s="3">
         <v>15400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-37200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-18700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1900</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-1700</v>
       </c>
       <c r="T26" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3300</v>
       </c>
-      <c r="E27" s="3">
-        <v>-6700</v>
-      </c>
       <c r="F27" s="3">
-        <v>-16300</v>
+        <v>-6600</v>
       </c>
       <c r="G27" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="H27" s="3">
         <v>-1500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-600</v>
       </c>
-      <c r="I27" s="3">
-        <v>-6700</v>
-      </c>
       <c r="J27" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="K27" s="3">
         <v>15400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-37200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-18700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1900</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-1700</v>
       </c>
       <c r="T27" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,8 +2049,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1991,35 +2061,35 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1100</v>
       </c>
-      <c r="F32" s="3">
-        <v>10200</v>
-      </c>
       <c r="G32" s="3">
-        <v>-5900</v>
+        <v>10000</v>
       </c>
       <c r="H32" s="3">
-        <v>-6600</v>
+        <v>-5800</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-6500</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-20400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>34100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-11100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2033,69 +2103,75 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3300</v>
       </c>
-      <c r="E33" s="3">
-        <v>-6700</v>
-      </c>
       <c r="F33" s="3">
-        <v>-16300</v>
+        <v>-6600</v>
       </c>
       <c r="G33" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="H33" s="3">
         <v>-1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-600</v>
       </c>
-      <c r="I33" s="3">
-        <v>-6700</v>
-      </c>
       <c r="J33" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="K33" s="3">
         <v>15400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-37200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-18700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1900</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-1700</v>
       </c>
       <c r="T33" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3300</v>
       </c>
-      <c r="E35" s="3">
-        <v>-6700</v>
-      </c>
       <c r="F35" s="3">
-        <v>-16300</v>
+        <v>-6600</v>
       </c>
       <c r="G35" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="H35" s="3">
         <v>-1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-600</v>
       </c>
-      <c r="I35" s="3">
-        <v>-6700</v>
-      </c>
       <c r="J35" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="K35" s="3">
         <v>15400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-37200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-18700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1900</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-1700</v>
       </c>
       <c r="T35" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,44 +2397,45 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>29200</v>
+        <v>18500</v>
       </c>
       <c r="E41" s="3">
-        <v>38700</v>
+        <v>28800</v>
       </c>
       <c r="F41" s="3">
-        <v>46100</v>
+        <v>38100</v>
       </c>
       <c r="G41" s="3">
-        <v>51500</v>
+        <v>45300</v>
       </c>
       <c r="H41" s="3">
-        <v>56500</v>
+        <v>50700</v>
       </c>
       <c r="I41" s="3">
-        <v>61200</v>
+        <v>55500</v>
       </c>
       <c r="J41" s="3">
+        <v>60300</v>
+      </c>
+      <c r="K41" s="3">
         <v>66000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>75000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>77300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>34100</v>
       </c>
-      <c r="N41" s="3">
-        <v>0</v>
-      </c>
       <c r="O41" s="3">
         <v>0</v>
       </c>
@@ -2356,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="Q41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R41" s="3">
         <v>100</v>
@@ -2365,10 +2452,13 @@
         <v>100</v>
       </c>
       <c r="T41" s="3">
+        <v>100</v>
+      </c>
+      <c r="U41" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2423,8 +2513,11 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2479,8 +2572,11 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2535,52 +2631,55 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7800</v>
+        <v>6400</v>
       </c>
       <c r="E45" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F45" s="3">
         <v>1800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3">
-        <v>1800</v>
-      </c>
       <c r="I45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J45" s="3">
         <v>2300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>200</v>
       </c>
       <c r="R45" s="3">
         <v>200</v>
@@ -2589,45 +2688,48 @@
         <v>200</v>
       </c>
       <c r="T45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>37100</v>
+        <v>24900</v>
       </c>
       <c r="E46" s="3">
-        <v>40600</v>
+        <v>36500</v>
       </c>
       <c r="F46" s="3">
-        <v>46700</v>
+        <v>39900</v>
       </c>
       <c r="G46" s="3">
-        <v>52600</v>
+        <v>45900</v>
       </c>
       <c r="H46" s="3">
-        <v>58200</v>
+        <v>51700</v>
       </c>
       <c r="I46" s="3">
-        <v>63600</v>
+        <v>57300</v>
       </c>
       <c r="J46" s="3">
+        <v>62600</v>
+      </c>
+      <c r="K46" s="3">
         <v>66500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>75500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>78000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>35300</v>
-      </c>
-      <c r="N46" s="3">
-        <v>400</v>
       </c>
       <c r="O46" s="3">
         <v>400</v>
@@ -2636,7 +2738,7 @@
         <v>400</v>
       </c>
       <c r="Q46" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="R46" s="3">
         <v>300</v>
@@ -2645,10 +2747,13 @@
         <v>300</v>
       </c>
       <c r="T46" s="3">
+        <v>300</v>
+      </c>
+      <c r="U46" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2703,8 +2808,11 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2759,8 +2867,11 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2792,7 +2903,7 @@
         <v>300</v>
       </c>
       <c r="M49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N49" s="3">
         <v>400</v>
@@ -2804,7 +2915,7 @@
         <v>400</v>
       </c>
       <c r="Q49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="R49" s="3">
         <v>300</v>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,8 +3044,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2983,8 +3103,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,43 +3162,46 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>37400</v>
+        <v>25200</v>
       </c>
       <c r="E54" s="3">
-        <v>40900</v>
+        <v>36800</v>
       </c>
       <c r="F54" s="3">
-        <v>47000</v>
+        <v>40200</v>
       </c>
       <c r="G54" s="3">
-        <v>52900</v>
+        <v>46200</v>
       </c>
       <c r="H54" s="3">
-        <v>58600</v>
+        <v>52000</v>
       </c>
       <c r="I54" s="3">
-        <v>63900</v>
+        <v>57600</v>
       </c>
       <c r="J54" s="3">
+        <v>62900</v>
+      </c>
+      <c r="K54" s="3">
         <v>66800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>75900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>78400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>35700</v>
-      </c>
-      <c r="N54" s="3">
-        <v>800</v>
       </c>
       <c r="O54" s="3">
         <v>800</v>
@@ -3084,7 +3210,7 @@
         <v>800</v>
       </c>
       <c r="Q54" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="R54" s="3">
         <v>600</v>
@@ -3093,10 +3219,13 @@
         <v>600</v>
       </c>
       <c r="T54" s="3">
+        <v>600</v>
+      </c>
+      <c r="U54" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,64 +3269,68 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2500</v>
+        <v>1400</v>
       </c>
       <c r="E57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F57" s="3">
         <v>1900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>900</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1300</v>
       </c>
       <c r="H57" s="3">
         <v>1300</v>
       </c>
       <c r="I57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
-      </c>
-      <c r="N57" s="3">
-        <v>5900</v>
       </c>
       <c r="O57" s="3">
         <v>5900</v>
       </c>
       <c r="P57" s="3">
+        <v>5900</v>
+      </c>
+      <c r="Q57" s="3">
         <v>6000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3231,28 +3365,31 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>700</v>
-      </c>
-      <c r="O58" s="3">
-        <v>400</v>
       </c>
       <c r="P58" s="3">
         <v>400</v>
       </c>
       <c r="Q58" s="3">
+        <v>400</v>
+      </c>
+      <c r="R58" s="3">
         <v>300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>200</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3307,64 +3444,70 @@
       <c r="T59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2500</v>
+        <v>1400</v>
       </c>
       <c r="E60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F60" s="3">
         <v>1900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>900</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1300</v>
       </c>
       <c r="H60" s="3">
         <v>1300</v>
       </c>
       <c r="I60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J60" s="3">
         <v>500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3396,19 +3539,19 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3">
         <v>300</v>
       </c>
       <c r="O61" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P61" s="3">
         <v>200</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
@@ -3417,46 +3560,49 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>40100</v>
+        <v>20400</v>
       </c>
       <c r="E62" s="3">
+        <v>39400</v>
+      </c>
+      <c r="F62" s="3">
+        <v>46300</v>
+      </c>
+      <c r="G62" s="3">
         <v>47100</v>
       </c>
-      <c r="F62" s="3">
-        <v>47800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>37300</v>
-      </c>
       <c r="H62" s="3">
-        <v>43100</v>
+        <v>36700</v>
       </c>
       <c r="I62" s="3">
+        <v>42400</v>
+      </c>
+      <c r="J62" s="3">
         <v>400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>43400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>73100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>40200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11700</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3475,8 +3621,11 @@
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>42600</v>
+        <v>21500</v>
       </c>
       <c r="E66" s="3">
-        <v>49000</v>
+        <v>41900</v>
       </c>
       <c r="F66" s="3">
-        <v>48800</v>
+        <v>48200</v>
       </c>
       <c r="G66" s="3">
-        <v>38700</v>
+        <v>48000</v>
       </c>
       <c r="H66" s="3">
-        <v>44400</v>
+        <v>38000</v>
       </c>
       <c r="I66" s="3">
+        <v>43600</v>
+      </c>
+      <c r="J66" s="3">
         <v>900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>44200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>73700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>41000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6800</v>
-      </c>
-      <c r="O66" s="3">
-        <v>6600</v>
       </c>
       <c r="P66" s="3">
         <v>6600</v>
       </c>
       <c r="Q66" s="3">
+        <v>6600</v>
+      </c>
+      <c r="R66" s="3">
         <v>4400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-110900</v>
+        <v>-101000</v>
       </c>
       <c r="E72" s="3">
-        <v>-107600</v>
+        <v>-109100</v>
       </c>
       <c r="F72" s="3">
-        <v>-100900</v>
+        <v>-105900</v>
       </c>
       <c r="G72" s="3">
-        <v>-84500</v>
+        <v>-99200</v>
       </c>
       <c r="H72" s="3">
-        <v>-83000</v>
+        <v>-83200</v>
       </c>
       <c r="I72" s="3">
-        <v>-13600</v>
+        <v>-81700</v>
       </c>
       <c r="J72" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="K72" s="3">
         <v>-68600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-76600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-36400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-19300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-26700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-25600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-25200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-18600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-17900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-16000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-14400</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-5200</v>
+        <v>3700</v>
       </c>
       <c r="E76" s="3">
-        <v>-8100</v>
+        <v>-5100</v>
       </c>
       <c r="F76" s="3">
-        <v>-1800</v>
+        <v>-8000</v>
       </c>
       <c r="G76" s="3">
-        <v>14200</v>
+        <v>-1700</v>
       </c>
       <c r="H76" s="3">
-        <v>14200</v>
+        <v>14000</v>
       </c>
       <c r="I76" s="3">
-        <v>63000</v>
+        <v>14000</v>
       </c>
       <c r="J76" s="3">
+        <v>62000</v>
+      </c>
+      <c r="K76" s="3">
         <v>22600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>37400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>23500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-6000</v>
-      </c>
-      <c r="O76" s="3">
-        <v>-5800</v>
       </c>
       <c r="P76" s="3">
         <v>-5800</v>
       </c>
       <c r="Q76" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="R76" s="3">
         <v>-3800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-3000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-1100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3300</v>
       </c>
-      <c r="E81" s="3">
-        <v>-6700</v>
-      </c>
       <c r="F81" s="3">
-        <v>-16300</v>
+        <v>-6600</v>
       </c>
       <c r="G81" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="H81" s="3">
         <v>-1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-600</v>
       </c>
-      <c r="I81" s="3">
-        <v>-6700</v>
-      </c>
       <c r="J81" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="K81" s="3">
         <v>15400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-37200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-18700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1900</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-1700</v>
       </c>
       <c r="T81" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4618,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4476,8 +4675,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-15000</v>
+        <v>-10300</v>
       </c>
       <c r="E89" s="3">
-        <v>-7300</v>
+        <v>-14800</v>
       </c>
       <c r="F89" s="3">
-        <v>-5400</v>
+        <v>-7200</v>
       </c>
       <c r="G89" s="3">
-        <v>-4900</v>
+        <v>-5300</v>
       </c>
       <c r="H89" s="3">
-        <v>-4600</v>
+        <v>-4800</v>
       </c>
       <c r="I89" s="3">
-        <v>-6600</v>
+        <v>-4500</v>
       </c>
       <c r="J89" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="K89" s="3">
         <v>-3500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-10500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,8 +5054,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4890,8 +5111,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,8 +5229,11 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5058,8 +5288,11 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,64 +5547,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6800</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>87700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>44900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>900</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5393,83 +5642,89 @@
         <v>0</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-9500</v>
+        <v>-10300</v>
       </c>
       <c r="E102" s="3">
-        <v>-7300</v>
+        <v>-9400</v>
       </c>
       <c r="F102" s="3">
-        <v>-5400</v>
+        <v>-7200</v>
       </c>
       <c r="G102" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="H102" s="3">
         <v>-4900</v>
       </c>
-      <c r="H102" s="3">
-        <v>-4800</v>
-      </c>
       <c r="I102" s="3">
-        <v>-4800</v>
+        <v>-4700</v>
       </c>
       <c r="J102" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="K102" s="3">
         <v>-10300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>77300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>34100</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
         <v>0</v>
       </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>-100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>BCT</t>
   </si>
@@ -656,99 +656,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -806,8 +810,11 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -865,8 +872,11 @@
       <c r="U9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -924,8 +934,11 @@
       <c r="U10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,67 +960,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>9300</v>
+        <v>11300</v>
       </c>
       <c r="E12" s="3">
-        <v>7000</v>
+        <v>9400</v>
       </c>
       <c r="F12" s="3">
-        <v>5200</v>
+        <v>7100</v>
       </c>
       <c r="G12" s="3">
-        <v>4100</v>
+        <v>5300</v>
       </c>
       <c r="H12" s="3">
-        <v>4400</v>
+        <v>4200</v>
       </c>
       <c r="I12" s="3">
+        <v>4500</v>
+      </c>
+      <c r="J12" s="3">
         <v>4300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,16 +1082,19 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1082,11 +1102,11 @@
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1098,13 +1118,13 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N14" s="3">
         <v>200</v>
       </c>
       <c r="O14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1112,8 +1132,8 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>4</v>
@@ -1124,8 +1144,11 @@
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1156,8 +1179,8 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1180,11 +1203,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,67 +1229,71 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>11500</v>
+        <v>13500</v>
       </c>
       <c r="E17" s="3">
-        <v>10400</v>
+        <v>11700</v>
       </c>
       <c r="F17" s="3">
-        <v>7700</v>
+        <v>10600</v>
       </c>
       <c r="G17" s="3">
-        <v>6100</v>
+        <v>7800</v>
       </c>
       <c r="H17" s="3">
-        <v>7300</v>
+        <v>6200</v>
       </c>
       <c r="I17" s="3">
-        <v>7100</v>
+        <v>7400</v>
       </c>
       <c r="J17" s="3">
+        <v>7200</v>
+      </c>
+      <c r="K17" s="3">
         <v>6600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1271,58 +1301,61 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>-10400</v>
+        <v>-11700</v>
       </c>
       <c r="F18" s="3">
-        <v>-7700</v>
+        <v>-10600</v>
       </c>
       <c r="G18" s="3">
-        <v>-6100</v>
+        <v>-7800</v>
       </c>
       <c r="H18" s="3">
-        <v>-7300</v>
+        <v>-6200</v>
       </c>
       <c r="I18" s="3">
-        <v>-7100</v>
+        <v>-7400</v>
       </c>
       <c r="J18" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-6600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,8 +1377,9 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1353,38 +1387,38 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>7200</v>
+        <v>19800</v>
       </c>
       <c r="F20" s="3">
+        <v>7300</v>
+      </c>
+      <c r="G20" s="3">
         <v>1100</v>
       </c>
-      <c r="G20" s="3">
-        <v>-10000</v>
-      </c>
       <c r="H20" s="3">
-        <v>5800</v>
+        <v>-10100</v>
       </c>
       <c r="I20" s="3">
-        <v>6500</v>
+        <v>5900</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>20400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-34100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>11100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1398,13 +1432,16 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1412,66 +1449,69 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3300</v>
       </c>
-      <c r="F21" s="3">
-        <v>-6600</v>
-      </c>
       <c r="G21" s="3">
-        <v>-16100</v>
+        <v>-6700</v>
       </c>
       <c r="H21" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>15400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-37200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-18500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1900</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-1700</v>
       </c>
       <c r="U21" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1495,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
@@ -1504,7 +1544,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1521,67 +1561,73 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>8100</v>
+        <v>-15600</v>
       </c>
       <c r="E23" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3300</v>
       </c>
-      <c r="F23" s="3">
-        <v>-6600</v>
-      </c>
       <c r="G23" s="3">
-        <v>-16100</v>
+        <v>-6700</v>
       </c>
       <c r="H23" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="I23" s="3">
         <v>-1500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>15400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-37200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1900</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-1700</v>
       </c>
       <c r="U23" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1639,8 +1685,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>8100</v>
+        <v>-15600</v>
       </c>
       <c r="E26" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3300</v>
       </c>
-      <c r="F26" s="3">
-        <v>-6600</v>
-      </c>
       <c r="G26" s="3">
-        <v>-16100</v>
+        <v>-6700</v>
       </c>
       <c r="H26" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="I26" s="3">
         <v>-1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>15400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-37200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-18700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1900</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-1700</v>
       </c>
       <c r="U26" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>8100</v>
+        <v>-15500</v>
       </c>
       <c r="E27" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3300</v>
       </c>
-      <c r="F27" s="3">
-        <v>-6600</v>
-      </c>
       <c r="G27" s="3">
-        <v>-16100</v>
+        <v>-6700</v>
       </c>
       <c r="H27" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="I27" s="3">
         <v>-1500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>15400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-37200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-18700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1900</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-1700</v>
       </c>
       <c r="U27" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,8 +2119,11 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2061,38 +2131,38 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>-7200</v>
+        <v>-19800</v>
       </c>
       <c r="F32" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="G32" s="3">
         <v>-1100</v>
       </c>
-      <c r="G32" s="3">
-        <v>10000</v>
-      </c>
       <c r="H32" s="3">
-        <v>-5800</v>
+        <v>10100</v>
       </c>
       <c r="I32" s="3">
-        <v>-6500</v>
+        <v>-5900</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-6600</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-20400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>34100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-11100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2106,72 +2176,78 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>8100</v>
+        <v>-15500</v>
       </c>
       <c r="E33" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3300</v>
       </c>
-      <c r="F33" s="3">
-        <v>-6600</v>
-      </c>
       <c r="G33" s="3">
-        <v>-16100</v>
+        <v>-6700</v>
       </c>
       <c r="H33" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="I33" s="3">
         <v>-1500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>15400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-37200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-18700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1900</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-1700</v>
       </c>
       <c r="U33" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>8100</v>
+        <v>-15500</v>
       </c>
       <c r="E35" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3300</v>
       </c>
-      <c r="F35" s="3">
-        <v>-6600</v>
-      </c>
       <c r="G35" s="3">
-        <v>-16100</v>
+        <v>-6700</v>
       </c>
       <c r="H35" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="I35" s="3">
         <v>-1500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>15400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-37200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-18700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1900</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-1700</v>
       </c>
       <c r="U35" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,47 +2484,48 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>18500</v>
+        <v>8600</v>
       </c>
       <c r="E41" s="3">
-        <v>28800</v>
+        <v>18700</v>
       </c>
       <c r="F41" s="3">
-        <v>38100</v>
+        <v>29200</v>
       </c>
       <c r="G41" s="3">
-        <v>45300</v>
+        <v>38700</v>
       </c>
       <c r="H41" s="3">
-        <v>50700</v>
+        <v>46000</v>
       </c>
       <c r="I41" s="3">
-        <v>55500</v>
+        <v>51400</v>
       </c>
       <c r="J41" s="3">
+        <v>56300</v>
+      </c>
+      <c r="K41" s="3">
         <v>60300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>66000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>75000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>77300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>34100</v>
       </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
       <c r="P41" s="3">
         <v>0</v>
       </c>
@@ -2446,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="R41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S41" s="3">
         <v>100</v>
@@ -2455,10 +2542,13 @@
         <v>100</v>
       </c>
       <c r="U41" s="3">
+        <v>100</v>
+      </c>
+      <c r="V41" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2516,8 +2606,11 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2575,8 +2668,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2634,55 +2730,58 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6400</v>
+        <v>7500</v>
       </c>
       <c r="E45" s="3">
-        <v>7700</v>
+        <v>6500</v>
       </c>
       <c r="F45" s="3">
+        <v>7800</v>
+      </c>
+      <c r="G45" s="3">
         <v>1800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="I45" s="3">
-        <v>1700</v>
-      </c>
       <c r="J45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K45" s="3">
         <v>2300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
-      </c>
-      <c r="R45" s="3">
-        <v>200</v>
       </c>
       <c r="S45" s="3">
         <v>200</v>
@@ -2691,48 +2790,51 @@
         <v>200</v>
       </c>
       <c r="U45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>24900</v>
+        <v>16100</v>
       </c>
       <c r="E46" s="3">
-        <v>36500</v>
+        <v>25300</v>
       </c>
       <c r="F46" s="3">
-        <v>39900</v>
+        <v>37000</v>
       </c>
       <c r="G46" s="3">
-        <v>45900</v>
+        <v>40500</v>
       </c>
       <c r="H46" s="3">
-        <v>51700</v>
+        <v>46600</v>
       </c>
       <c r="I46" s="3">
-        <v>57300</v>
+        <v>52500</v>
       </c>
       <c r="J46" s="3">
+        <v>58100</v>
+      </c>
+      <c r="K46" s="3">
         <v>62600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>66500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>75500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>78000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>35300</v>
-      </c>
-      <c r="O46" s="3">
-        <v>400</v>
       </c>
       <c r="P46" s="3">
         <v>400</v>
@@ -2741,7 +2843,7 @@
         <v>400</v>
       </c>
       <c r="R46" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="S46" s="3">
         <v>300</v>
@@ -2750,15 +2852,18 @@
         <v>300</v>
       </c>
       <c r="U46" s="3">
+        <v>300</v>
+      </c>
+      <c r="V46" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E47" s="3">
         <v>0</v>
@@ -2811,8 +2916,11 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2870,8 +2978,11 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2906,7 +3017,7 @@
         <v>300</v>
       </c>
       <c r="N49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="O49" s="3">
         <v>400</v>
@@ -2918,7 +3029,7 @@
         <v>400</v>
       </c>
       <c r="R49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="S49" s="3">
         <v>300</v>
@@ -2929,8 +3040,11 @@
       <c r="U49" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,8 +3164,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3106,8 +3226,11 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,46 +3288,49 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>25200</v>
+        <v>16800</v>
       </c>
       <c r="E54" s="3">
-        <v>36800</v>
+        <v>25500</v>
       </c>
       <c r="F54" s="3">
-        <v>40200</v>
+        <v>37300</v>
       </c>
       <c r="G54" s="3">
-        <v>46200</v>
+        <v>40800</v>
       </c>
       <c r="H54" s="3">
-        <v>52000</v>
+        <v>46900</v>
       </c>
       <c r="I54" s="3">
-        <v>57600</v>
+        <v>52800</v>
       </c>
       <c r="J54" s="3">
+        <v>58400</v>
+      </c>
+      <c r="K54" s="3">
         <v>62900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>66800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>75900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>78400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35700</v>
-      </c>
-      <c r="O54" s="3">
-        <v>800</v>
       </c>
       <c r="P54" s="3">
         <v>800</v>
@@ -3213,7 +3339,7 @@
         <v>800</v>
       </c>
       <c r="R54" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="S54" s="3">
         <v>600</v>
@@ -3222,10 +3348,13 @@
         <v>600</v>
       </c>
       <c r="U54" s="3">
+        <v>600</v>
+      </c>
+      <c r="V54" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,67 +3400,71 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
-        <v>2400</v>
-      </c>
       <c r="F57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G57" s="3">
         <v>1900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>900</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1300</v>
       </c>
       <c r="I57" s="3">
         <v>1300</v>
       </c>
       <c r="J57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
-      </c>
-      <c r="O57" s="3">
-        <v>5900</v>
       </c>
       <c r="P57" s="3">
         <v>5900</v>
       </c>
       <c r="Q57" s="3">
+        <v>5900</v>
+      </c>
+      <c r="R57" s="3">
         <v>6000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3368,28 +3502,31 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>700</v>
-      </c>
-      <c r="P58" s="3">
-        <v>400</v>
       </c>
       <c r="Q58" s="3">
         <v>400</v>
       </c>
       <c r="R58" s="3">
+        <v>400</v>
+      </c>
+      <c r="S58" s="3">
         <v>300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>200</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3447,67 +3584,73 @@
       <c r="U59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1400</v>
       </c>
-      <c r="E60" s="3">
-        <v>2400</v>
-      </c>
       <c r="F60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G60" s="3">
         <v>1900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>900</v>
-      </c>
-      <c r="H60" s="3">
-        <v>1300</v>
       </c>
       <c r="I60" s="3">
         <v>1300</v>
       </c>
       <c r="J60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K60" s="3">
         <v>500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3542,19 +3685,19 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>300</v>
       </c>
       <c r="P61" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q61" s="3">
         <v>200</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
@@ -3563,49 +3706,52 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>20400</v>
+        <v>22800</v>
       </c>
       <c r="E62" s="3">
-        <v>39400</v>
+        <v>20700</v>
       </c>
       <c r="F62" s="3">
-        <v>46300</v>
+        <v>40000</v>
       </c>
       <c r="G62" s="3">
-        <v>47100</v>
+        <v>47000</v>
       </c>
       <c r="H62" s="3">
-        <v>36700</v>
+        <v>47700</v>
       </c>
       <c r="I62" s="3">
-        <v>42400</v>
+        <v>37200</v>
       </c>
       <c r="J62" s="3">
+        <v>43000</v>
+      </c>
+      <c r="K62" s="3">
         <v>400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>43400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>73100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>40200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11700</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3624,8 +3770,11 @@
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,67 +3956,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>21500</v>
+        <v>27900</v>
       </c>
       <c r="E66" s="3">
-        <v>41900</v>
+        <v>21800</v>
       </c>
       <c r="F66" s="3">
-        <v>48200</v>
+        <v>42500</v>
       </c>
       <c r="G66" s="3">
-        <v>48000</v>
+        <v>48900</v>
       </c>
       <c r="H66" s="3">
-        <v>38000</v>
+        <v>48600</v>
       </c>
       <c r="I66" s="3">
-        <v>43600</v>
+        <v>38600</v>
       </c>
       <c r="J66" s="3">
+        <v>44300</v>
+      </c>
+      <c r="K66" s="3">
         <v>900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>44200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>73700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>41000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6800</v>
-      </c>
-      <c r="P66" s="3">
-        <v>6600</v>
       </c>
       <c r="Q66" s="3">
         <v>6600</v>
       </c>
       <c r="R66" s="3">
+        <v>6600</v>
+      </c>
+      <c r="S66" s="3">
         <v>4400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,67 +4290,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-101000</v>
+        <v>-117900</v>
       </c>
       <c r="E72" s="3">
-        <v>-109100</v>
+        <v>-102400</v>
       </c>
       <c r="F72" s="3">
-        <v>-105900</v>
+        <v>-110700</v>
       </c>
       <c r="G72" s="3">
-        <v>-99200</v>
+        <v>-107400</v>
       </c>
       <c r="H72" s="3">
-        <v>-83200</v>
+        <v>-100600</v>
       </c>
       <c r="I72" s="3">
-        <v>-81700</v>
+        <v>-84300</v>
       </c>
       <c r="J72" s="3">
+        <v>-82800</v>
+      </c>
+      <c r="K72" s="3">
         <v>-13400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-68600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-76600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-36400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-19300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-26700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-25600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-25200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-18600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-17900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-16000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-14400</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4538,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E76" s="3">
         <v>3700</v>
       </c>
-      <c r="E76" s="3">
-        <v>-5100</v>
-      </c>
       <c r="F76" s="3">
-        <v>-8000</v>
+        <v>-5200</v>
       </c>
       <c r="G76" s="3">
-        <v>-1700</v>
+        <v>-8100</v>
       </c>
       <c r="H76" s="3">
-        <v>14000</v>
+        <v>-1800</v>
       </c>
       <c r="I76" s="3">
-        <v>14000</v>
+        <v>14200</v>
       </c>
       <c r="J76" s="3">
+        <v>14200</v>
+      </c>
+      <c r="K76" s="3">
         <v>62000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>37400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-6000</v>
-      </c>
-      <c r="P76" s="3">
-        <v>-5800</v>
       </c>
       <c r="Q76" s="3">
         <v>-5800</v>
       </c>
       <c r="R76" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="S76" s="3">
         <v>-3800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-3000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-1100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>8100</v>
+        <v>-15500</v>
       </c>
       <c r="E81" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3300</v>
       </c>
-      <c r="F81" s="3">
-        <v>-6600</v>
-      </c>
       <c r="G81" s="3">
-        <v>-16100</v>
+        <v>-6700</v>
       </c>
       <c r="H81" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="I81" s="3">
         <v>-1500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>15400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-37200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-18700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1900</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-1700</v>
       </c>
       <c r="U81" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,8 +4817,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4678,8 +4877,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-10300</v>
+        <v>-10200</v>
       </c>
       <c r="E89" s="3">
-        <v>-14800</v>
+        <v>-10400</v>
       </c>
       <c r="F89" s="3">
-        <v>-7200</v>
+        <v>-15000</v>
       </c>
       <c r="G89" s="3">
-        <v>-5300</v>
+        <v>-7300</v>
       </c>
       <c r="H89" s="3">
-        <v>-4800</v>
+        <v>-5400</v>
       </c>
       <c r="I89" s="3">
-        <v>-4500</v>
+        <v>-4900</v>
       </c>
       <c r="J89" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="K89" s="3">
         <v>-6500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,8 +5275,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5114,8 +5335,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,8 +5459,11 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5291,8 +5521,11 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5547,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,8 +5793,11 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5559,58 +5805,61 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6800</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>87700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>44900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>900</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5645,86 +5894,92 @@
         <v>0</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-1100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="K102" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="L102" s="3">
         <v>-10300</v>
       </c>
-      <c r="E102" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-10300</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>77300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>34100</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
         <v>0</v>
       </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
         <v>0</v>
       </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>-100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>BCT</t>
   </si>
@@ -656,103 +656,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -813,8 +816,11 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -875,8 +881,11 @@
       <c r="V9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -937,8 +946,11 @@
       <c r="V10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,70 +973,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>11300</v>
+        <v>10400</v>
       </c>
       <c r="E12" s="3">
-        <v>9400</v>
+        <v>11200</v>
       </c>
       <c r="F12" s="3">
-        <v>7100</v>
+        <v>9300</v>
       </c>
       <c r="G12" s="3">
-        <v>5300</v>
+        <v>7000</v>
       </c>
       <c r="H12" s="3">
-        <v>4200</v>
+        <v>5200</v>
       </c>
       <c r="I12" s="3">
-        <v>4500</v>
+        <v>4100</v>
       </c>
       <c r="J12" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K12" s="3">
         <v>4300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,8 +1101,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1096,8 +1115,8 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -1105,11 +1124,11 @@
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1121,13 +1140,13 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O14" s="3">
         <v>200</v>
       </c>
       <c r="P14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1135,8 +1154,8 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
@@ -1147,8 +1166,11 @@
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1182,8 +1204,8 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1206,11 +1228,14 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,70 +1255,74 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13500</v>
+        <v>12500</v>
       </c>
       <c r="E17" s="3">
-        <v>11700</v>
+        <v>13400</v>
       </c>
       <c r="F17" s="3">
-        <v>10600</v>
+        <v>11600</v>
       </c>
       <c r="G17" s="3">
-        <v>7800</v>
+        <v>10500</v>
       </c>
       <c r="H17" s="3">
-        <v>6200</v>
+        <v>7700</v>
       </c>
       <c r="I17" s="3">
-        <v>7400</v>
+        <v>6100</v>
       </c>
       <c r="J17" s="3">
+        <v>7300</v>
+      </c>
+      <c r="K17" s="3">
         <v>7200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1301,61 +1330,64 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>-11700</v>
+        <v>-13400</v>
       </c>
       <c r="F18" s="3">
-        <v>-10600</v>
+        <v>-11600</v>
       </c>
       <c r="G18" s="3">
-        <v>-7800</v>
+        <v>-10500</v>
       </c>
       <c r="H18" s="3">
-        <v>-6200</v>
+        <v>-7700</v>
       </c>
       <c r="I18" s="3">
-        <v>-7400</v>
+        <v>-6100</v>
       </c>
       <c r="J18" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-7200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-9600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,8 +1410,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1387,41 +1420,41 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>19800</v>
+        <v>-2000</v>
       </c>
       <c r="F20" s="3">
-        <v>7300</v>
+        <v>19600</v>
       </c>
       <c r="G20" s="3">
+        <v>7200</v>
+      </c>
+      <c r="H20" s="3">
         <v>1100</v>
       </c>
-      <c r="H20" s="3">
-        <v>-10100</v>
-      </c>
       <c r="I20" s="3">
-        <v>5900</v>
+        <v>-10000</v>
       </c>
       <c r="J20" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K20" s="3">
         <v>6600</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>20400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-34100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>11100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1435,13 +1468,16 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1449,61 +1485,64 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
-        <v>8200</v>
+        <v>-15400</v>
       </c>
       <c r="F21" s="3">
+        <v>8100</v>
+      </c>
+      <c r="G21" s="3">
         <v>-3300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-6700</v>
-      </c>
       <c r="H21" s="3">
-        <v>-16300</v>
+        <v>-6600</v>
       </c>
       <c r="I21" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="J21" s="3">
         <v>-1500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>15400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-37200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-18500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1900</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-1700</v>
       </c>
       <c r="V21" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1513,8 +1552,8 @@
       <c r="E22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -1538,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
@@ -1547,7 +1586,7 @@
         <v>100</v>
       </c>
       <c r="Q22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1564,70 +1603,76 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-15600</v>
+        <v>2300</v>
       </c>
       <c r="E23" s="3">
-        <v>8200</v>
+        <v>-15400</v>
       </c>
       <c r="F23" s="3">
+        <v>8100</v>
+      </c>
+      <c r="G23" s="3">
         <v>-3300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6700</v>
       </c>
-      <c r="H23" s="3">
-        <v>-16300</v>
-      </c>
       <c r="I23" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="J23" s="3">
         <v>-1500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>15400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-37200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1900</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-1700</v>
       </c>
       <c r="V23" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1688,8 +1733,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-15600</v>
+        <v>2300</v>
       </c>
       <c r="E26" s="3">
-        <v>8200</v>
+        <v>-15400</v>
       </c>
       <c r="F26" s="3">
+        <v>8100</v>
+      </c>
+      <c r="G26" s="3">
         <v>-3300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6700</v>
       </c>
-      <c r="H26" s="3">
-        <v>-16300</v>
-      </c>
       <c r="I26" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="J26" s="3">
         <v>-1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>15400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-37200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-18700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1900</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-1700</v>
       </c>
       <c r="V26" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-15500</v>
+        <v>2300</v>
       </c>
       <c r="E27" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="F27" s="3">
         <v>8200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6700</v>
       </c>
-      <c r="H27" s="3">
-        <v>-16300</v>
-      </c>
       <c r="I27" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="J27" s="3">
         <v>-1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>15400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-37200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1900</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-1700</v>
       </c>
       <c r="V27" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,8 +2188,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2131,41 +2200,41 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>-19800</v>
+        <v>2000</v>
       </c>
       <c r="F32" s="3">
-        <v>-7300</v>
+        <v>-19600</v>
       </c>
       <c r="G32" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1100</v>
       </c>
-      <c r="H32" s="3">
-        <v>10100</v>
-      </c>
       <c r="I32" s="3">
-        <v>-5900</v>
+        <v>10000</v>
       </c>
       <c r="J32" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="K32" s="3">
         <v>-6600</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-20400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>34100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-11100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2179,75 +2248,81 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-15500</v>
+        <v>2300</v>
       </c>
       <c r="E33" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="F33" s="3">
         <v>8200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6700</v>
       </c>
-      <c r="H33" s="3">
-        <v>-16300</v>
-      </c>
       <c r="I33" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="J33" s="3">
         <v>-1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>15400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-37200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1900</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-1700</v>
       </c>
       <c r="V33" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-15500</v>
+        <v>2300</v>
       </c>
       <c r="E35" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="F35" s="3">
         <v>8200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6700</v>
       </c>
-      <c r="H35" s="3">
-        <v>-16300</v>
-      </c>
       <c r="I35" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="J35" s="3">
         <v>-1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>15400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-37200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1900</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-1700</v>
       </c>
       <c r="V35" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,50 +2570,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>8600</v>
+        <v>1300</v>
       </c>
       <c r="E41" s="3">
-        <v>18700</v>
+        <v>8500</v>
       </c>
       <c r="F41" s="3">
-        <v>29200</v>
+        <v>18500</v>
       </c>
       <c r="G41" s="3">
-        <v>38700</v>
+        <v>28900</v>
       </c>
       <c r="H41" s="3">
-        <v>46000</v>
+        <v>38300</v>
       </c>
       <c r="I41" s="3">
-        <v>51400</v>
+        <v>45500</v>
       </c>
       <c r="J41" s="3">
+        <v>50900</v>
+      </c>
+      <c r="K41" s="3">
         <v>56300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>60300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>66000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>75000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>77300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>34100</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
       <c r="Q41" s="3">
         <v>0</v>
       </c>
@@ -2536,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T41" s="3">
         <v>100</v>
@@ -2545,10 +2631,13 @@
         <v>100</v>
       </c>
       <c r="V41" s="3">
+        <v>100</v>
+      </c>
+      <c r="W41" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2609,8 +2698,11 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2671,8 +2763,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2733,58 +2828,61 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7500</v>
+        <v>6200</v>
       </c>
       <c r="E45" s="3">
-        <v>6500</v>
+        <v>7400</v>
       </c>
       <c r="F45" s="3">
-        <v>7800</v>
+        <v>6400</v>
       </c>
       <c r="G45" s="3">
+        <v>7700</v>
+      </c>
+      <c r="H45" s="3">
         <v>1800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
-      </c>
-      <c r="S45" s="3">
-        <v>200</v>
       </c>
       <c r="T45" s="3">
         <v>200</v>
@@ -2793,51 +2891,54 @@
         <v>200</v>
       </c>
       <c r="V45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>16100</v>
+        <v>7500</v>
       </c>
       <c r="E46" s="3">
-        <v>25300</v>
+        <v>16000</v>
       </c>
       <c r="F46" s="3">
-        <v>37000</v>
+        <v>25000</v>
       </c>
       <c r="G46" s="3">
-        <v>40500</v>
+        <v>36600</v>
       </c>
       <c r="H46" s="3">
-        <v>46600</v>
+        <v>40100</v>
       </c>
       <c r="I46" s="3">
-        <v>52500</v>
+        <v>46100</v>
       </c>
       <c r="J46" s="3">
+        <v>51900</v>
+      </c>
+      <c r="K46" s="3">
         <v>58100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>62600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>66500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>75500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>78000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>35300</v>
-      </c>
-      <c r="P46" s="3">
-        <v>400</v>
       </c>
       <c r="Q46" s="3">
         <v>400</v>
@@ -2846,7 +2947,7 @@
         <v>400</v>
       </c>
       <c r="S46" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T46" s="3">
         <v>300</v>
@@ -2855,19 +2956,22 @@
         <v>300</v>
       </c>
       <c r="V46" s="3">
+        <v>300</v>
+      </c>
+      <c r="W46" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>600</v>
+      </c>
+      <c r="E47" s="3">
         <v>400</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
       <c r="F47" s="3">
         <v>0</v>
       </c>
@@ -2919,8 +3023,11 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2981,8 +3088,11 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3020,7 +3130,7 @@
         <v>300</v>
       </c>
       <c r="O49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="P49" s="3">
         <v>400</v>
@@ -3032,7 +3142,7 @@
         <v>400</v>
       </c>
       <c r="S49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T49" s="3">
         <v>300</v>
@@ -3043,8 +3153,11 @@
       <c r="V49" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,8 +3283,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3229,8 +3348,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,49 +3413,52 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>16800</v>
+        <v>8400</v>
       </c>
       <c r="E54" s="3">
-        <v>25500</v>
+        <v>16600</v>
       </c>
       <c r="F54" s="3">
-        <v>37300</v>
+        <v>25300</v>
       </c>
       <c r="G54" s="3">
-        <v>40800</v>
+        <v>36900</v>
       </c>
       <c r="H54" s="3">
-        <v>46900</v>
+        <v>40400</v>
       </c>
       <c r="I54" s="3">
-        <v>52800</v>
+        <v>46400</v>
       </c>
       <c r="J54" s="3">
+        <v>52200</v>
+      </c>
+      <c r="K54" s="3">
         <v>58400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>62900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>66800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>75900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>78400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35700</v>
-      </c>
-      <c r="P54" s="3">
-        <v>800</v>
       </c>
       <c r="Q54" s="3">
         <v>800</v>
@@ -3342,7 +3467,7 @@
         <v>800</v>
       </c>
       <c r="S54" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="T54" s="3">
         <v>600</v>
@@ -3351,10 +3476,13 @@
         <v>600</v>
       </c>
       <c r="V54" s="3">
+        <v>600</v>
+      </c>
+      <c r="W54" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,70 +3530,74 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>5400</v>
+        <v>9200</v>
       </c>
       <c r="E57" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
-        <v>2500</v>
-      </c>
       <c r="G57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H57" s="3">
         <v>1900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1300</v>
       </c>
       <c r="J57" s="3">
         <v>1300</v>
       </c>
       <c r="K57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
-      </c>
-      <c r="P57" s="3">
-        <v>5900</v>
       </c>
       <c r="Q57" s="3">
         <v>5900</v>
       </c>
       <c r="R57" s="3">
+        <v>5900</v>
+      </c>
+      <c r="S57" s="3">
         <v>6000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3505,28 +3638,31 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>700</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>400</v>
       </c>
       <c r="R58" s="3">
         <v>400</v>
       </c>
       <c r="S58" s="3">
+        <v>400</v>
+      </c>
+      <c r="T58" s="3">
         <v>300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>200</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3587,70 +3723,76 @@
       <c r="V59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>5400</v>
+        <v>9200</v>
       </c>
       <c r="E60" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F60" s="3">
         <v>1400</v>
       </c>
-      <c r="F60" s="3">
-        <v>2500</v>
-      </c>
       <c r="G60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H60" s="3">
         <v>1900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>900</v>
-      </c>
-      <c r="I60" s="3">
-        <v>1300</v>
       </c>
       <c r="J60" s="3">
         <v>1300</v>
       </c>
       <c r="K60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L60" s="3">
         <v>500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3688,19 +3830,19 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>300</v>
       </c>
       <c r="Q61" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R61" s="3">
         <v>200</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -3709,52 +3851,55 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>22800</v>
+        <v>7700</v>
       </c>
       <c r="E62" s="3">
-        <v>20700</v>
+        <v>22600</v>
       </c>
       <c r="F62" s="3">
-        <v>40000</v>
+        <v>20500</v>
       </c>
       <c r="G62" s="3">
-        <v>47000</v>
+        <v>39600</v>
       </c>
       <c r="H62" s="3">
-        <v>47700</v>
+        <v>46500</v>
       </c>
       <c r="I62" s="3">
-        <v>37200</v>
+        <v>47200</v>
       </c>
       <c r="J62" s="3">
+        <v>36900</v>
+      </c>
+      <c r="K62" s="3">
         <v>43000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>43400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>73100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>40200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11700</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3773,8 +3918,11 @@
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>27900</v>
+        <v>16500</v>
       </c>
       <c r="E66" s="3">
-        <v>21800</v>
+        <v>27600</v>
       </c>
       <c r="F66" s="3">
-        <v>42500</v>
+        <v>21600</v>
       </c>
       <c r="G66" s="3">
-        <v>48900</v>
+        <v>42000</v>
       </c>
       <c r="H66" s="3">
-        <v>48600</v>
+        <v>48400</v>
       </c>
       <c r="I66" s="3">
-        <v>38600</v>
+        <v>48100</v>
       </c>
       <c r="J66" s="3">
+        <v>38200</v>
+      </c>
+      <c r="K66" s="3">
         <v>44300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>44200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>73700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>41000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6800</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>6600</v>
       </c>
       <c r="R66" s="3">
         <v>6600</v>
       </c>
       <c r="S66" s="3">
+        <v>6600</v>
+      </c>
+      <c r="T66" s="3">
         <v>4400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-117900</v>
+        <v>-102500</v>
       </c>
       <c r="E72" s="3">
-        <v>-102400</v>
+        <v>-105300</v>
       </c>
       <c r="F72" s="3">
-        <v>-110700</v>
+        <v>-90700</v>
       </c>
       <c r="G72" s="3">
-        <v>-107400</v>
+        <v>-99500</v>
       </c>
       <c r="H72" s="3">
-        <v>-100600</v>
+        <v>-96900</v>
       </c>
       <c r="I72" s="3">
-        <v>-84300</v>
+        <v>-90700</v>
       </c>
       <c r="J72" s="3">
+        <v>-74900</v>
+      </c>
+      <c r="K72" s="3">
         <v>-82800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-13400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-68600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-76600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-36400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-19300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-26700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-25600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-25200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-18600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-17900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-16000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-14400</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-11100</v>
+        <v>-8100</v>
       </c>
       <c r="E76" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="F76" s="3">
         <v>3700</v>
       </c>
-      <c r="F76" s="3">
-        <v>-5200</v>
-      </c>
       <c r="G76" s="3">
-        <v>-8100</v>
+        <v>-5100</v>
       </c>
       <c r="H76" s="3">
-        <v>-1800</v>
+        <v>-8000</v>
       </c>
       <c r="I76" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J76" s="3">
+        <v>14000</v>
+      </c>
+      <c r="K76" s="3">
         <v>14200</v>
       </c>
-      <c r="J76" s="3">
-        <v>14200</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>62000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>37400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-6000</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>-5800</v>
       </c>
       <c r="R76" s="3">
         <v>-5800</v>
       </c>
       <c r="S76" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="T76" s="3">
         <v>-3800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-3000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-1100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-15500</v>
+        <v>2300</v>
       </c>
       <c r="E81" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="F81" s="3">
         <v>8200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6700</v>
       </c>
-      <c r="H81" s="3">
-        <v>-16300</v>
-      </c>
       <c r="I81" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="J81" s="3">
         <v>-1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>15400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-37200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1900</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-1700</v>
       </c>
       <c r="V81" s="3">
         <v>-1700</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,8 +5015,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4880,8 +5078,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-10200</v>
+        <v>-6900</v>
       </c>
       <c r="E89" s="3">
-        <v>-10400</v>
+        <v>-10100</v>
       </c>
       <c r="F89" s="3">
-        <v>-15000</v>
+        <v>-10300</v>
       </c>
       <c r="G89" s="3">
-        <v>-7300</v>
+        <v>-14800</v>
       </c>
       <c r="H89" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="I89" s="3">
         <v>-5400</v>
       </c>
-      <c r="I89" s="3">
-        <v>-4900</v>
-      </c>
       <c r="J89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="K89" s="3">
         <v>-4600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,8 +5495,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5338,8 +5558,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,8 +5688,11 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5524,8 +5753,11 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5610,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,70 +6038,76 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6800</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>87700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>44900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>900</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5897,89 +6145,95 @@
         <v>0</v>
       </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-1100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-10200</v>
+        <v>-7200</v>
       </c>
       <c r="E102" s="3">
-        <v>-10400</v>
+        <v>-10100</v>
       </c>
       <c r="F102" s="3">
-        <v>-9500</v>
+        <v>-10300</v>
       </c>
       <c r="G102" s="3">
-        <v>-7300</v>
+        <v>-9400</v>
       </c>
       <c r="H102" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="I102" s="3">
         <v>-5400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>77300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>34100</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
         <v>0</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
         <v>0</v>
       </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-700</v>
       </c>
     </row>
